--- a/tests/fixtures/cmdb/topdesk-missing-appid.xlsx
+++ b/tests/fixtures/cmdb/topdesk-missing-appid.xlsx
@@ -3,9 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAEA186-9AA1-40C3-AE4A-D564E2BAA450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51480" yWindow="5280" windowWidth="29040" windowHeight="15840" tabRatio="594" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="51480" yWindow="5280" windowWidth="29040" windowHeight="15840" tabRatio="594" firstSheet="1"/>
   </bookViews>
   <sheets>
     <sheet name="Invoer AIA data" sheetId="6" r:id="rId1"/>
@@ -19,18 +18,6 @@
     <sheet name="Blad3" sheetId="4" r:id="rId9"/>
     <sheet name="Origineel" sheetId="1" r:id="rId10"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Behandelgroepen!$A$1:$E$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Beheerde Applicaties CMDB'!$A$1:$AP$1066</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Blad3!$A$1:$A$128</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Gearchiveerde Applicaties'!$A$1:$I$434</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Invoer AIA data'!$A$1:$BB$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Invoer APP data'!$A$1:$CD$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Invoer gearchiveerde appl'!$A$1:$CO$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Onbeh Applicaties CMDB'!$A$1:$AH$98</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Origineel!$A$2:$AA$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Relatie APP oplosgroepen'!$B$2:$APJ$2</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1363,7 +1350,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C8FFAE6-2986-4F38-9797-2552E7727FDA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:AZ249"/>
   <sheetFormatPr defaultColWidth="20.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2708,17 +2695,17 @@
       <c r="C249" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BB1" xr:uid="{6C8FFAE6-2986-4F38-9797-2552E7727FDA}"/>
+  <autoFilter ref="A1:BB1"/>
   <hyperlinks>
-    <hyperlink ref="J2" r:id="rId1" display="mailto:letter.achternaam@gemeente.nl" xr:uid="{92E263F2-1000-4547-B807-F14BED24D8E1}"/>
+    <hyperlink ref="J2" r:id="rId1" display="mailto:letter.achternaam@gemeente.nl"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:AA1141"/>
   <sheetFormatPr defaultColWidth="214.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -33755,14 +33742,14 @@
       <c r="AA1141" s="10"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AA2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:AA2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F26ADF-A76E-483E-B515-1BC07834D443}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:AI100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -34417,9 +34404,9 @@
       <c r="AF100" s="18"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AH98" xr:uid="{B2F26ADF-A76E-483E-B515-1BC07834D443}"/>
+  <autoFilter ref="A1:AH1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <ignoredErrors>
     <ignoredError xmlns:x16r3="http://schemas.microsoft.com/office/spreadsheetml/2018/08/main" sqref="AF2" x16r3:misleadingFormat="1"/>
   </ignoredErrors>
@@ -34427,7 +34414,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7279925-5FC1-4109-A23D-8ADA8308449E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:CD1136"/>
   <sheetFormatPr defaultColWidth="27.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -47418,18 +47405,18 @@
       <c r="AD1136" s="11"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CD1" xr:uid="{C7279925-5FC1-4109-A23D-8ADA8308449E}"/>
+  <autoFilter ref="A1:CD1"/>
   <hyperlinks>
-    <hyperlink ref="O2" r:id="rId1" xr:uid="{7EFA633E-E1C5-4984-B2ED-623F21986EA4}"/>
-    <hyperlink ref="U2" r:id="rId2" xr:uid="{56D610AE-976A-4756-8D98-54457789B785}"/>
+    <hyperlink ref="O2" r:id="rId1"/>
+    <hyperlink ref="U2" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FA9F2C5-2A80-40F0-ABC6-EC876C3BEE48}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:AP1068"/>
   <sheetFormatPr defaultColWidth="45.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -57369,19 +57356,15 @@
       <c r="Y1068" s="18"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP1066" xr:uid="{5FA9F2C5-2A80-40F0-ABC6-EC876C3BEE48}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A852:AP852">
-      <sortCondition ref="K1:K1062"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:AP1"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4764C0-EEB6-43A1-977A-04CBD0DD848C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:CO2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -58042,21 +58025,21 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CO1" xr:uid="{CA4764C0-EEB6-43A1-977A-04CBD0DD848C}"/>
+  <autoFilter ref="A1:CO1"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="J2" r:id="rId1" display="mailto:letter.achternaam@gemeente.nl" xr:uid="{1B6002AF-D815-4999-B25E-78F8BBCD6D43}"/>
-    <hyperlink ref="O2" r:id="rId2" display="mailto:letter.achternaam@gemeente.nl" xr:uid="{95346917-3E80-4EA3-A1B1-C4C7E6722FC6}"/>
-    <hyperlink ref="P2" r:id="rId3" xr:uid="{66E98122-A82B-4238-940E-1F641D831B4C}"/>
-    <hyperlink ref="U2" r:id="rId4" display="mailto:letter.achternaam@gemeente.nl" xr:uid="{46576A51-1928-42FD-8F76-9ACFEE814F94}"/>
+    <hyperlink ref="J2" r:id="rId1" display="mailto:letter.achternaam@gemeente.nl"/>
+    <hyperlink ref="O2" r:id="rId2" display="mailto:letter.achternaam@gemeente.nl"/>
+    <hyperlink ref="P2" r:id="rId3"/>
+    <hyperlink ref="U2" r:id="rId4" display="mailto:letter.achternaam@gemeente.nl"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F31C3127-42FF-46D7-A7BE-D6B327F344FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:I466"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -59994,14 +59977,14 @@
       <c r="I466" s="27"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I434" xr:uid="{F31C3127-42FF-46D7-A7BE-D6B327F344FD}"/>
+  <autoFilter ref="A1:I1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C58AFA-DED0-476A-AD3C-1E5843262B11}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:AMY3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -63149,14 +63132,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:APJ2" xr:uid="{D4C58AFA-DED0-476A-AD3C-1E5843262B11}"/>
+  <autoFilter ref="B2:APJ2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE148F3A-2307-4656-B058-576ECC862847}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:D1095"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -66605,18 +66588,14 @@
       <c r="A1095"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E98" xr:uid="{FE148F3A-2307-4656-B058-576ECC862847}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D98">
-      <sortCondition ref="A1:A98"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:E1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5015BD4B-87F1-492F-B21B-0961C7B7BBA9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -66656,12 +66635,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A128" xr:uid="{5015BD4B-87F1-492F-B21B-0961C7B7BBA9}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A128">
-      <sortCondition ref="A1:A128"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:A1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>